--- a/results/model_results_diabetes.xlsx
+++ b/results/model_results_diabetes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,11 @@
           <t>Time (s)</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Data_norm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -513,6 +518,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,8 +549,9 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2217473983764648</v>
-      </c>
+        <v>2.084424018859863</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -581,6 +588,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -611,8 +619,9 @@
         <v>0.01</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3648335933685303</v>
-      </c>
+        <v>0.03968596458435059</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -649,6 +658,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -679,8 +689,9 @@
         <v>0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>0.36370849609375</v>
-      </c>
+        <v>0.03653097152709961</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,6 +728,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -747,8 +759,9 @@
         <v>0.1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3963470458984375</v>
-      </c>
+        <v>0.03932690620422363</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -785,6 +798,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -815,8 +829,9 @@
         <v>0.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.302152156829834</v>
-      </c>
+        <v>0.03993916511535645</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -853,6 +868,7 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,8 +899,9 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2834415435791016</v>
-      </c>
+        <v>0.03714990615844727</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -921,6 +938,7 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -951,8 +969,9 @@
         <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2893579006195068</v>
-      </c>
+        <v>0.04213500022888184</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -989,6 +1008,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1019,8 +1039,9 @@
         <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2870175838470459</v>
-      </c>
+        <v>0.03885293006896973</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1057,6 +1078,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1093,6 +1115,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1129,6 +1152,7 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1165,6 +1189,7 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1201,6 +1226,7 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1237,6 +1263,7 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1273,6 +1300,294 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.3855421686746988</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="G25" t="n">
+        <v>48</v>
+      </c>
+      <c r="H25" t="n">
+        <v>51</v>
+      </c>
+      <c r="I25" t="n">
+        <v>23</v>
+      </c>
+      <c r="J25" t="n">
+        <v>32</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0.00185704231262207</v>
+      </c>
+      <c r="M25" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6168831168831169</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5354330708661418</v>
+      </c>
+      <c r="G26" t="n">
+        <v>61</v>
+      </c>
+      <c r="H26" t="n">
+        <v>38</v>
+      </c>
+      <c r="I26" t="n">
+        <v>21</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0.001212835311889648</v>
+      </c>
+      <c r="M26" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7402597402597403</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.6491228070175439</v>
+      </c>
+      <c r="G27" t="n">
+        <v>77</v>
+      </c>
+      <c r="H27" t="n">
+        <v>22</v>
+      </c>
+      <c r="I27" t="n">
+        <v>18</v>
+      </c>
+      <c r="J27" t="n">
+        <v>37</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0.0007979869842529297</v>
+      </c>
+      <c r="M27" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G28" t="n">
+        <v>81</v>
+      </c>
+      <c r="H28" t="n">
+        <v>18</v>
+      </c>
+      <c r="I28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" t="n">
+        <v>35</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0.0006909370422363281</v>
+      </c>
+      <c r="M28" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G29" t="n">
+        <v>81</v>
+      </c>
+      <c r="H29" t="n">
+        <v>18</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20</v>
+      </c>
+      <c r="J29" t="n">
+        <v>35</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0.0006930828094482422</v>
+      </c>
+      <c r="M29" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>50</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G30" t="n">
+        <v>81</v>
+      </c>
+      <c r="H30" t="n">
+        <v>18</v>
+      </c>
+      <c r="I30" t="n">
+        <v>20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>35</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0.0006458759307861328</v>
+      </c>
+      <c r="M30" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>100</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.6542056074766355</v>
+      </c>
+      <c r="G31" t="n">
+        <v>82</v>
+      </c>
+      <c r="H31" t="n">
+        <v>17</v>
+      </c>
+      <c r="I31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" t="n">
+        <v>35</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0.0006401538848876953</v>
+      </c>
+      <c r="M31" t="n">
+        <v>8.602929272067815</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/model_results_diabetes.xlsx
+++ b/results/model_results_diabetes.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,71 +425,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Epsilon</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>F1 Score</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best C</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Data_norm</t>
         </is>
@@ -530,26 +542,26 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.767119818739171</v>
+        <v>0.7686938127974617</v>
       </c>
       <c r="D3" t="n">
-        <v>0.708249734136831</v>
+        <v>0.7120545849918914</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5679955703211517</v>
+        <v>0.5722943722943723</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6293664285993052</v>
+        <v>0.6317615326537022</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>2.084424018859863</v>
+        <v>0.1891074180603027</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
@@ -560,7 +572,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="C4" t="n">
         <v>0.6428571428571429</v>
@@ -597,7 +609,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="C5" t="n">
         <v>0.6531200423056583</v>
@@ -619,7 +631,7 @@
         <v>0.01</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03968596458435059</v>
+        <v>0.1811532974243164</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
@@ -630,7 +642,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C6" t="n">
         <v>0.6428571428571429</v>
@@ -667,7 +679,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C7" t="n">
         <v>0.6531200423056583</v>
@@ -689,7 +701,7 @@
         <v>0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03653097152709961</v>
+        <v>0.1640524864196777</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
@@ -700,19 +712,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6753246753246753</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>99</v>
@@ -721,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -737,29 +749,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6645425700687466</v>
+        <v>0.6531200423056583</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5513702963702964</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2348484848484849</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3276751946607342</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03932690620422363</v>
+        <v>0.170628547668457</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
@@ -770,31 +782,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8125</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4727272727272727</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5977011494252874</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -807,29 +819,29 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7152035959809624</v>
+        <v>0.6531200423056583</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6583997873471558</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3854978354978356</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4824891774891774</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03993916511535645</v>
+        <v>0.1577472686767578</v>
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
@@ -840,31 +852,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7597402597402597</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="D12" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6181818181818182</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6476190476190476</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="J12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -877,29 +889,29 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7607086197778953</v>
+        <v>0.6547593865679534</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6931432748538012</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5640692640692639</v>
+        <v>0.004761904761904761</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6200182368603422</v>
+        <v>0.00909090909090909</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03714990615844727</v>
+        <v>0.145085334777832</v>
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
@@ -910,31 +922,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7597402597402597</v>
+        <v>0.6623376623376623</v>
       </c>
       <c r="D14" t="n">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6181818181818182</v>
+        <v>0.05454545454545454</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6476190476190476</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="G14" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="J14" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -947,29 +959,29 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7541248016922263</v>
+        <v>0.6580380750925436</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6864880952380952</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.554112554112554</v>
+        <v>0.07077922077922079</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6109334546497577</v>
+        <v>0.1178575712143928</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>0.01</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04213500022888184</v>
+        <v>0.1338362693786621</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
@@ -980,31 +992,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7532467532467533</v>
+        <v>0.6948051948051948</v>
       </c>
       <c r="D16" t="n">
-        <v>0.660377358490566</v>
+        <v>0.7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.2545454545454545</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6481481481481481</v>
+        <v>0.3733333333333334</v>
       </c>
       <c r="G16" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J16" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1017,58 +1029,58 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7686144896879956</v>
+        <v>0.703569539925965</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7060631860399662</v>
+        <v>0.6347127872127872</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5764069264069264</v>
+        <v>0.346969696969697</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6314643523565218</v>
+        <v>0.4434781949437122</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03885293006896973</v>
+        <v>0.152329683303833</v>
       </c>
       <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6037735849056604</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="E18" t="n">
         <v>0.5818181818181818</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.6464646464646465</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H18" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
         <v>23</v>
@@ -1083,38 +1095,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Input_hpt</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7662337662337663</v>
+        <v>0.7035430988894765</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.6124212715389186</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.4082251082251082</v>
       </c>
       <c r="F19" t="n">
-        <v>0.660377358490566</v>
-      </c>
-      <c r="G19" t="n">
-        <v>83</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="n">
-        <v>20</v>
-      </c>
-      <c r="J19" t="n">
-        <v>35</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+        <v>0.4847742608268923</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1715774536132812</v>
+      </c>
       <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1124,31 +1132,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7662337662337663</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.4909090909090909</v>
       </c>
       <c r="F20" t="n">
-        <v>0.660377358490566</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="G20" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1161,31 +1169,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7662337662337663</v>
+        <v>0.6688311688311688</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.54</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.4909090909090909</v>
       </c>
       <c r="F21" t="n">
-        <v>0.660377358490566</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="G21" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H21" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1198,31 +1206,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>0.7662337662337663</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="F22" t="n">
-        <v>0.660377358490566</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="G22" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1235,25 +1243,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7662337662337663</v>
+        <v>0.7597402597402597</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="E23" t="n">
         <v>0.6363636363636364</v>
       </c>
       <c r="F23" t="n">
-        <v>0.660377358490566</v>
+        <v>0.6542056074766355</v>
       </c>
       <c r="G23" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
         <v>20</v>
@@ -1272,7 +1280,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C24" t="n">
         <v>0.7662337662337663</v>
@@ -1305,125 +1313,113 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1</v>
+        <v>30</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5194805194805194</v>
+        <v>0.7662337662337663</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3855421686746988</v>
+        <v>0.6862745098039216</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5818181818181818</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="F25" t="n">
-        <v>0.463768115942029</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="G25" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="H25" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>0.00185704231262207</v>
-      </c>
-      <c r="M25" t="n">
-        <v>8.602929272067815</v>
-      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6168831168831169</v>
+        <v>0.7662337662337663</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.6862745098039216</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6181818181818182</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5354330708661418</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="G26" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="H26" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>0.001212835311889648</v>
-      </c>
-      <c r="M26" t="n">
-        <v>8.602929272067815</v>
-      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7402597402597403</v>
+        <v>0.7662337662337663</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6271186440677966</v>
+        <v>0.6862745098039216</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6727272727272727</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6491228070175439</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="G27" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H27" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>0.0007979869842529297</v>
-      </c>
-      <c r="M27" t="n">
-        <v>8.602929272067815</v>
-      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1432,35 +1428,35 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>0.01</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7532467532467533</v>
+        <v>0.5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.660377358490566</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5818181818181818</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6481481481481481</v>
+        <v>0.4539007092198581</v>
       </c>
       <c r="G28" t="n">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="H28" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>0.0006909370422363281</v>
+        <v>0.00536036491394043</v>
       </c>
       <c r="M28" t="n">
         <v>8.602929272067815</v>
@@ -1473,35 +1469,35 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>0.1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7532467532467533</v>
+        <v>0.5194805194805194</v>
       </c>
       <c r="D29" t="n">
-        <v>0.660377358490566</v>
+        <v>0.3855421686746988</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5818181818181818</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6481481481481481</v>
+        <v>0.463768115942029</v>
       </c>
       <c r="G29" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="H29" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>0.0006930828094482422</v>
+        <v>0.004352331161499023</v>
       </c>
       <c r="M29" t="n">
         <v>8.602929272067815</v>
@@ -1514,35 +1510,35 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7532467532467533</v>
+        <v>0.6168831168831169</v>
       </c>
       <c r="D30" t="n">
-        <v>0.660377358490566</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6481481481481481</v>
+        <v>0.5354330708661418</v>
       </c>
       <c r="G30" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="H30" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>0.0006458759307861328</v>
+        <v>0.008368253707885742</v>
       </c>
       <c r="M30" t="n">
         <v>8.602929272067815</v>
@@ -1555,38 +1551,1456 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7597402597402597</v>
+        <v>0.7402597402597403</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6730769230769231</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6727272727272727</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6542056074766355</v>
+        <v>0.6491228070175439</v>
       </c>
       <c r="G31" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>0.0006401538848876953</v>
+        <v>0.009657382965087891</v>
       </c>
       <c r="M31" t="n">
         <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G32" t="n">
+        <v>81</v>
+      </c>
+      <c r="H32" t="n">
+        <v>18</v>
+      </c>
+      <c r="I32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" t="n">
+        <v>35</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0.005885839462280273</v>
+      </c>
+      <c r="M32" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G33" t="n">
+        <v>81</v>
+      </c>
+      <c r="H33" t="n">
+        <v>18</v>
+      </c>
+      <c r="I33" t="n">
+        <v>20</v>
+      </c>
+      <c r="J33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0.005216121673583984</v>
+      </c>
+      <c r="M33" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>50</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="G34" t="n">
+        <v>81</v>
+      </c>
+      <c r="H34" t="n">
+        <v>18</v>
+      </c>
+      <c r="I34" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" t="n">
+        <v>35</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0.005365848541259766</v>
+      </c>
+      <c r="M34" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>100</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.6542056074766355</v>
+      </c>
+      <c r="G35" t="n">
+        <v>82</v>
+      </c>
+      <c r="H35" t="n">
+        <v>17</v>
+      </c>
+      <c r="I35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J35" t="n">
+        <v>35</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0.004624128341674805</v>
+      </c>
+      <c r="M35" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Original_balanced</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="G36" t="n">
+        <v>70</v>
+      </c>
+      <c r="H36" t="n">
+        <v>29</v>
+      </c>
+      <c r="I36" t="n">
+        <v>16</v>
+      </c>
+      <c r="J36" t="n">
+        <v>39</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Original_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7580864197530864</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.7699513341864489</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7379268292682927</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.7521315494016425</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>9.332996606826782</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.2924528301886792</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5636363636363636</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.3850931677018634</v>
+      </c>
+      <c r="G38" t="n">
+        <v>24</v>
+      </c>
+      <c r="H38" t="n">
+        <v>75</v>
+      </c>
+      <c r="I38" t="n">
+        <v>24</v>
+      </c>
+      <c r="J38" t="n">
+        <v>31</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5050925925925925</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.5070815030614326</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.4913414634146341</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.4979828720396897</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2130093574523926</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.3557046979865772</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9636363636363636</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5196078431372549</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>96</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="n">
+        <v>53</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5235956790123456</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.524787137713967</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5382926829268292</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5297054609173129</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1612517833709717</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5844155844155844</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="G42" t="n">
+        <v>70</v>
+      </c>
+      <c r="H42" t="n">
+        <v>29</v>
+      </c>
+      <c r="I42" t="n">
+        <v>35</v>
+      </c>
+      <c r="J42" t="n">
+        <v>20</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.512608024691358</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.5133915097678164</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.4990243902439025</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.5043343153604443</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1781787872314453</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.6558441558441559</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.1636363636363636</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.2535211267605634</v>
+      </c>
+      <c r="G44" t="n">
+        <v>92</v>
+      </c>
+      <c r="H44" t="n">
+        <v>7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>46</v>
+      </c>
+      <c r="J44" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.5086882716049382</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.5080551717710621</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.506219512195122</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5048097594241943</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.1826472282409668</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.6883116883116883</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.1636363636363636</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="G46" t="n">
+        <v>97</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>46</v>
+      </c>
+      <c r="J46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.5326543209876544</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.5339051868753881</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.5016463414634147</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5151991797775588</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1714863777160645</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>30</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.7337662337662337</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.594059405940594</v>
+      </c>
+      <c r="G48" t="n">
+        <v>83</v>
+      </c>
+      <c r="H48" t="n">
+        <v>16</v>
+      </c>
+      <c r="I48" t="n">
+        <v>25</v>
+      </c>
+      <c r="J48" t="n">
+        <v>30</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>30</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.5822067901234568</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.5876833482718898</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.5659146341463415</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5750093570321206</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.1891634464263916</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>50</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6545454545454545</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="G50" t="n">
+        <v>73</v>
+      </c>
+      <c r="H50" t="n">
+        <v>26</v>
+      </c>
+      <c r="I50" t="n">
+        <v>19</v>
+      </c>
+      <c r="J50" t="n">
+        <v>36</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.6745987654320988</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.6801925363121885</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.663170731707317</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.6700756115529123</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.1735367774963379</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>100</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7207792207792207</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.6504065040650406</v>
+      </c>
+      <c r="G52" t="n">
+        <v>71</v>
+      </c>
+      <c r="H52" t="n">
+        <v>28</v>
+      </c>
+      <c r="I52" t="n">
+        <v>15</v>
+      </c>
+      <c r="J52" t="n">
+        <v>40</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>100</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7033179012345678</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.7160185157323167</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6833536585365854</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.6972012029301897</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.2039341926574707</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6103896103896104</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4603174603174603</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5272727272727272</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.4915254237288136</v>
+      </c>
+      <c r="G54" t="n">
+        <v>65</v>
+      </c>
+      <c r="H54" t="n">
+        <v>34</v>
+      </c>
+      <c r="I54" t="n">
+        <v>26</v>
+      </c>
+      <c r="J54" t="n">
+        <v>29</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6883116883116883</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G55" t="n">
+        <v>66</v>
+      </c>
+      <c r="H55" t="n">
+        <v>33</v>
+      </c>
+      <c r="I55" t="n">
+        <v>15</v>
+      </c>
+      <c r="J55" t="n">
+        <v>40</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="G56" t="n">
+        <v>70</v>
+      </c>
+      <c r="H56" t="n">
+        <v>29</v>
+      </c>
+      <c r="I56" t="n">
+        <v>16</v>
+      </c>
+      <c r="J56" t="n">
+        <v>39</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="G57" t="n">
+        <v>70</v>
+      </c>
+      <c r="H57" t="n">
+        <v>29</v>
+      </c>
+      <c r="I57" t="n">
+        <v>16</v>
+      </c>
+      <c r="J57" t="n">
+        <v>39</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="G58" t="n">
+        <v>70</v>
+      </c>
+      <c r="H58" t="n">
+        <v>29</v>
+      </c>
+      <c r="I58" t="n">
+        <v>16</v>
+      </c>
+      <c r="J58" t="n">
+        <v>39</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>30</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="G59" t="n">
+        <v>70</v>
+      </c>
+      <c r="H59" t="n">
+        <v>29</v>
+      </c>
+      <c r="I59" t="n">
+        <v>16</v>
+      </c>
+      <c r="J59" t="n">
+        <v>39</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>50</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="G60" t="n">
+        <v>70</v>
+      </c>
+      <c r="H60" t="n">
+        <v>29</v>
+      </c>
+      <c r="I60" t="n">
+        <v>16</v>
+      </c>
+      <c r="J60" t="n">
+        <v>39</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>100</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="G61" t="n">
+        <v>70</v>
+      </c>
+      <c r="H61" t="n">
+        <v>29</v>
+      </c>
+      <c r="I61" t="n">
+        <v>16</v>
+      </c>
+      <c r="J61" t="n">
+        <v>39</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.512987012987013</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.3780487804878049</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.5636363636363636</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.4525547445255474</v>
+      </c>
+      <c r="G62" t="n">
+        <v>48</v>
+      </c>
+      <c r="H62" t="n">
+        <v>51</v>
+      </c>
+      <c r="I62" t="n">
+        <v>24</v>
+      </c>
+      <c r="J62" t="n">
+        <v>31</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>0.004433155059814453</v>
+      </c>
+      <c r="M62" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.538961038961039</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.4024390243902439</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.4817518248175183</v>
+      </c>
+      <c r="G63" t="n">
+        <v>50</v>
+      </c>
+      <c r="H63" t="n">
+        <v>49</v>
+      </c>
+      <c r="I63" t="n">
+        <v>22</v>
+      </c>
+      <c r="J63" t="n">
+        <v>33</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>0.004160404205322266</v>
+      </c>
+      <c r="M63" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.6298701298701299</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.4878048780487805</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.583941605839416</v>
+      </c>
+      <c r="G64" t="n">
+        <v>57</v>
+      </c>
+      <c r="H64" t="n">
+        <v>42</v>
+      </c>
+      <c r="I64" t="n">
+        <v>15</v>
+      </c>
+      <c r="J64" t="n">
+        <v>40</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>0.006627321243286133</v>
+      </c>
+      <c r="M64" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.7012987012987013</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.5616438356164384</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.7454545454545455</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="G65" t="n">
+        <v>67</v>
+      </c>
+      <c r="H65" t="n">
+        <v>32</v>
+      </c>
+      <c r="I65" t="n">
+        <v>14</v>
+      </c>
+      <c r="J65" t="n">
+        <v>41</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>0.007369041442871094</v>
+      </c>
+      <c r="M65" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>10</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.6948051948051948</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.6299212598425197</v>
+      </c>
+      <c r="G66" t="n">
+        <v>67</v>
+      </c>
+      <c r="H66" t="n">
+        <v>32</v>
+      </c>
+      <c r="I66" t="n">
+        <v>15</v>
+      </c>
+      <c r="J66" t="n">
+        <v>40</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>0.006760835647583008</v>
+      </c>
+      <c r="M66" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>30</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.582089552238806</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="G67" t="n">
+        <v>71</v>
+      </c>
+      <c r="H67" t="n">
+        <v>28</v>
+      </c>
+      <c r="I67" t="n">
+        <v>16</v>
+      </c>
+      <c r="J67" t="n">
+        <v>39</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>0.005927801132202148</v>
+      </c>
+      <c r="M67" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>50</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="G68" t="n">
+        <v>70</v>
+      </c>
+      <c r="H68" t="n">
+        <v>29</v>
+      </c>
+      <c r="I68" t="n">
+        <v>16</v>
+      </c>
+      <c r="J68" t="n">
+        <v>39</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>0.008686304092407227</v>
+      </c>
+      <c r="M68" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>100</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="G69" t="n">
+        <v>70</v>
+      </c>
+      <c r="H69" t="n">
+        <v>29</v>
+      </c>
+      <c r="I69" t="n">
+        <v>16</v>
+      </c>
+      <c r="J69" t="n">
+        <v>39</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>0.006041765213012695</v>
+      </c>
+      <c r="M69" t="n">
+        <v>8.381499661996164</v>
       </c>
     </row>
   </sheetData>

--- a/results/model_results_diabetes.xlsx
+++ b/results/model_results_diabetes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,55 +429,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Row_ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>F1 Score</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Best C</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Time (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Data_norm</t>
         </is>
@@ -486,1106 +491,1944 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Original_oversampled</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.7662337662337663</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.7077922077922078</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="F2" t="n">
-        <v>0.660377358490566</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="H2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J2" t="n">
         <v>16</v>
       </c>
-      <c r="I2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" t="n">
-        <v>35</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>39</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Original_hpt</t>
+          <t>Original_hpt_oversampled</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.767119818739171</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.708249734136831</v>
+        <v>0.7568478260869564</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5679955703211517</v>
+        <v>0.7682364470901648</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6293664285993052</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>0.7357407407407408</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7511149685395835</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>2.084424018859863</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.706299781799316</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_oversampled</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.1</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.6428571428571429</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.2470588235294118</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.3818181818181818</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="K4" t="n">
+        <v>21</v>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.1</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.6531200423056583</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.5087962962962963</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.5103360272477919</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>0.4964024390243902</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5016814270982224</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
         <v>0.01</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.03968596458435059</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0.06141495704650879</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_oversampled</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.6428571428571429</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.6623376623376623</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.07272727272727272</v>
       </c>
       <c r="G6" t="n">
-        <v>99</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I6" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.6531200423056583</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.5236265432098766</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.5240972166036991</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>0.4809146341463415</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4989227159337587</v>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
         <v>0.01</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.03653097152709961</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0.05149197578430176</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_oversampled</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>5</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.6753246753246753</v>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.7792207792207793</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.6545454545454545</v>
       </c>
       <c r="G8" t="n">
-        <v>99</v>
+        <v>0.6792452830188679</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="K8" t="n">
+        <v>36</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.6645425700687466</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.5513702963702964</v>
+        <v>0.6358950617283951</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2348484848484849</v>
+        <v>0.6424755176359798</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3276751946607342</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>0.6107317073170732</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6253612290923319</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.03932690620422363</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.06120395660400391</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_oversampled</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>10</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.7727272727272727</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.8125</v>
+        <v>0.7077922077922078</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4727272727272727</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5977011494252874</v>
+        <v>0.6909090909090909</v>
       </c>
       <c r="G10" t="n">
-        <v>93</v>
+        <v>0.628099173553719</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="I10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="K10" t="n">
+        <v>38</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7152035959809624</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6583997873471558</v>
+        <v>0.7662337662337663</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3854978354978356</v>
+        <v>0.6862745098039216</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4824891774891774</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H11" t="n">
+        <v>83</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20</v>
+      </c>
       <c r="K11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.03993916511535645</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_oversampled</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>30</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.7597402597402597</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.68</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6181818181818182</v>
+        <v>0.5774647887323944</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6476190476190476</v>
+        <v>0.7454545454545455</v>
       </c>
       <c r="G12" t="n">
-        <v>83</v>
+        <v>0.6507936507936508</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="K12" t="n">
+        <v>41</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>30</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.7607086197778953</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6931432748538012</v>
+        <v>0.756929012345679</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5640692640692639</v>
+        <v>0.7705517493017493</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6200182368603422</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+        <v>0.7379878048780488</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7519291134919421</v>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>0.03714990615844727</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.06700682640075684</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_oversampled</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>50</v>
       </c>
-      <c r="C14" t="n">
-        <v>0.7597402597402597</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.68</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6181818181818182</v>
+        <v>0.582089552238806</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6476190476190476</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="G14" t="n">
-        <v>83</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="H14" t="n">
+        <v>71</v>
+      </c>
+      <c r="I14" t="n">
+        <v>28</v>
+      </c>
+      <c r="J14" t="n">
         <v>16</v>
       </c>
-      <c r="I14" t="n">
-        <v>21</v>
-      </c>
-      <c r="J14" t="n">
-        <v>34</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>39</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>50</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.7541248016922263</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6864880952380952</v>
+        <v>0.7443672839506172</v>
       </c>
       <c r="E15" t="n">
-        <v>0.554112554112554</v>
+        <v>0.7569972923612485</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6109334546497577</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+        <v>0.723048780487805</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7381732856730927</v>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
         <v>10</v>
       </c>
-      <c r="L15" t="n">
-        <v>0.04213500022888184</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0.2077450752258301</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input_oversampled</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>100</v>
       </c>
-      <c r="C16" t="n">
-        <v>0.7532467532467533</v>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.660377358490566</v>
+        <v>0.7077922077922078</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6481481481481481</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="G16" t="n">
-        <v>81</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>35</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="K16" t="n">
+        <v>39</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Input_hpt</t>
+          <t>Input_hpt_oversampled</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>100</v>
       </c>
-      <c r="C17" t="n">
-        <v>0.7686144896879956</v>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.7060631860399662</v>
+        <v>0.756820987654321</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5764069264069264</v>
+        <v>0.7682672311331882</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6314643523565218</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>0.7404268292682927</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7522219157952454</v>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>10</v>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.03885293006896973</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.08070516586303711</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.1</v>
       </c>
-      <c r="C18" t="n">
-        <v>0.7142857142857143</v>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6037735849056604</v>
+        <v>0.7077922077922078</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5818181818181818</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.6909090909090909</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>0.628099173553719</v>
       </c>
       <c r="H18" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>32</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="K18" t="n">
+        <v>38</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" t="n">
-        <v>0.7662337662337663</v>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.7012987012987013</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="F19" t="n">
-        <v>0.660377358490566</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>0.6290322580645161</v>
       </c>
       <c r="H19" t="n">
+        <v>69</v>
+      </c>
+      <c r="I19" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" t="n">
         <v>16</v>
       </c>
-      <c r="I19" t="n">
-        <v>20</v>
-      </c>
-      <c r="J19" t="n">
-        <v>35</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>39</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>5</v>
       </c>
-      <c r="C20" t="n">
-        <v>0.7662337662337663</v>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.7077922077922078</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="F20" t="n">
-        <v>0.660377358490566</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="G20" t="n">
-        <v>83</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="H20" t="n">
+        <v>70</v>
+      </c>
+      <c r="I20" t="n">
+        <v>29</v>
+      </c>
+      <c r="J20" t="n">
         <v>16</v>
       </c>
-      <c r="I20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" t="n">
-        <v>35</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>39</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>10</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.7662337662337663</v>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.7077922077922078</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="F21" t="n">
-        <v>0.660377358490566</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="G21" t="n">
-        <v>83</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="H21" t="n">
+        <v>70</v>
+      </c>
+      <c r="I21" t="n">
+        <v>29</v>
+      </c>
+      <c r="J21" t="n">
         <v>16</v>
       </c>
-      <c r="I21" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" t="n">
-        <v>35</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>39</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>30</v>
       </c>
-      <c r="C22" t="n">
-        <v>0.7662337662337663</v>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.7077922077922078</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="F22" t="n">
-        <v>0.660377358490566</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="G22" t="n">
-        <v>83</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="H22" t="n">
+        <v>70</v>
+      </c>
+      <c r="I22" t="n">
+        <v>29</v>
+      </c>
+      <c r="J22" t="n">
         <v>16</v>
       </c>
-      <c r="I22" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" t="n">
-        <v>35</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>39</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>50</v>
       </c>
-      <c r="C23" t="n">
-        <v>0.7662337662337663</v>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.7077922077922078</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="F23" t="n">
-        <v>0.660377358490566</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="G23" t="n">
-        <v>83</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="H23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I23" t="n">
+        <v>29</v>
+      </c>
+      <c r="J23" t="n">
         <v>16</v>
       </c>
-      <c r="I23" t="n">
-        <v>20</v>
-      </c>
-      <c r="J23" t="n">
-        <v>35</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>39</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output_oversampled</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>100</v>
       </c>
-      <c r="C24" t="n">
-        <v>0.7662337662337663</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.7077922077922078</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="F24" t="n">
-        <v>0.660377358490566</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="G24" t="n">
-        <v>83</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="H24" t="n">
+        <v>70</v>
+      </c>
+      <c r="I24" t="n">
+        <v>29</v>
+      </c>
+      <c r="J24" t="n">
         <v>16</v>
       </c>
-      <c r="I24" t="n">
-        <v>20</v>
-      </c>
-      <c r="J24" t="n">
-        <v>35</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>39</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Original_hpt</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.5194805194805194</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>0.3855421686746988</v>
+        <v>0.767119818739171</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5818181818181818</v>
+        <v>0.708249734136831</v>
       </c>
       <c r="F25" t="n">
-        <v>0.463768115942029</v>
+        <v>0.5679955703211517</v>
       </c>
       <c r="G25" t="n">
-        <v>48</v>
-      </c>
-      <c r="H25" t="n">
-        <v>51</v>
-      </c>
-      <c r="I25" t="n">
-        <v>23</v>
-      </c>
-      <c r="J25" t="n">
-        <v>32</v>
-      </c>
+        <v>0.6293664285993052</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.00185704231262207</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>8.602929272067815</v>
-      </c>
+        <v>2.763554811477661</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.6168831168831169</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6181818181818182</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5354330708661418</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>34</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>0.001212835311889648</v>
-      </c>
-      <c r="M26" t="n">
-        <v>8.602929272067815</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Input_hpt</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.7402597402597403</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>0.6271186440677966</v>
+        <v>0.6531200423056583</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6727272727272727</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6491228070175439</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>77</v>
-      </c>
-      <c r="H27" t="n">
-        <v>22</v>
-      </c>
-      <c r="I27" t="n">
-        <v>18</v>
-      </c>
-      <c r="J27" t="n">
-        <v>37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>0.0007979869842529297</v>
+        <v>0.01</v>
       </c>
       <c r="M27" t="n">
-        <v>8.602929272067815</v>
-      </c>
+        <v>0.05453681945800781</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.7532467532467533</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>0.660377358490566</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6363636363636364</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6481481481481481</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>35</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>0.0006909370422363281</v>
-      </c>
-      <c r="M28" t="n">
-        <v>8.602929272067815</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Input_hpt</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.7532467532467533</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>0.660377358490566</v>
+        <v>0.6531200423056583</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6363636363636364</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6481481481481481</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>81</v>
-      </c>
-      <c r="H29" t="n">
-        <v>18</v>
-      </c>
-      <c r="I29" t="n">
-        <v>20</v>
-      </c>
-      <c r="J29" t="n">
-        <v>35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>0.0006930828094482422</v>
+        <v>0.01</v>
       </c>
       <c r="M29" t="n">
-        <v>8.602929272067815</v>
-      </c>
+        <v>0.0498650074005127</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0.6753246753246753</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="H30" t="n">
+        <v>99</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>50</v>
       </c>
-      <c r="C30" t="n">
-        <v>0.7532467532467533</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.660377358490566</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.6481481481481481</v>
-      </c>
-      <c r="G30" t="n">
-        <v>81</v>
-      </c>
-      <c r="H30" t="n">
-        <v>18</v>
-      </c>
-      <c r="I30" t="n">
-        <v>20</v>
-      </c>
-      <c r="J30" t="n">
-        <v>35</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>0.0006458759307861328</v>
-      </c>
-      <c r="M30" t="n">
-        <v>8.602929272067815</v>
-      </c>
+      <c r="K30" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Input_hpt</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>100</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.7597402597402597</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>0.6730769230769231</v>
+        <v>0.6645425700687466</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5513702963702964</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6542056074766355</v>
+        <v>0.2348484848484849</v>
       </c>
       <c r="G31" t="n">
-        <v>82</v>
-      </c>
-      <c r="H31" t="n">
-        <v>17</v>
-      </c>
-      <c r="I31" t="n">
-        <v>20</v>
-      </c>
-      <c r="J31" t="n">
-        <v>35</v>
-      </c>
+        <v>0.3276751946607342</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>0.0006401538848876953</v>
+        <v>0.1</v>
       </c>
       <c r="M31" t="n">
+        <v>0.05227494239807129</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.4727272727272727</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5977011494252874</v>
+      </c>
+      <c r="H32" t="n">
+        <v>93</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>29</v>
+      </c>
+      <c r="K32" t="n">
+        <v>26</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0.7152035959809624</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6583997873471558</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.3854978354978356</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.4824891774891774</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.05733990669250488</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.6476190476190476</v>
+      </c>
+      <c r="H34" t="n">
+        <v>83</v>
+      </c>
+      <c r="I34" t="n">
+        <v>16</v>
+      </c>
+      <c r="J34" t="n">
+        <v>21</v>
+      </c>
+      <c r="K34" t="n">
+        <v>34</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0.7607086197778953</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6931432748538012</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5640692640692639</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.6200182368603422</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.05182385444641113</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>50</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.6476190476190476</v>
+      </c>
+      <c r="H36" t="n">
+        <v>83</v>
+      </c>
+      <c r="I36" t="n">
+        <v>16</v>
+      </c>
+      <c r="J36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K36" t="n">
+        <v>34</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>50</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0.7541248016922263</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6864880952380952</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.554112554112554</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.6109334546497577</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>10</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.05637717247009277</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>100</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H38" t="n">
+        <v>81</v>
+      </c>
+      <c r="I38" t="n">
+        <v>18</v>
+      </c>
+      <c r="J38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" t="n">
+        <v>35</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>100</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>0.7686144896879956</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7060631860399662</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5764069264069264</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.6314643523565218</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>10</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.05215311050415039</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6037735849056604</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="H40" t="n">
+        <v>78</v>
+      </c>
+      <c r="I40" t="n">
+        <v>21</v>
+      </c>
+      <c r="J40" t="n">
+        <v>23</v>
+      </c>
+      <c r="K40" t="n">
+        <v>32</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H41" t="n">
+        <v>83</v>
+      </c>
+      <c r="I41" t="n">
+        <v>16</v>
+      </c>
+      <c r="J41" t="n">
+        <v>20</v>
+      </c>
+      <c r="K41" t="n">
+        <v>35</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H42" t="n">
+        <v>83</v>
+      </c>
+      <c r="I42" t="n">
+        <v>16</v>
+      </c>
+      <c r="J42" t="n">
+        <v>20</v>
+      </c>
+      <c r="K42" t="n">
+        <v>35</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H43" t="n">
+        <v>83</v>
+      </c>
+      <c r="I43" t="n">
+        <v>16</v>
+      </c>
+      <c r="J43" t="n">
+        <v>20</v>
+      </c>
+      <c r="K43" t="n">
+        <v>35</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>30</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H44" t="n">
+        <v>83</v>
+      </c>
+      <c r="I44" t="n">
+        <v>16</v>
+      </c>
+      <c r="J44" t="n">
+        <v>20</v>
+      </c>
+      <c r="K44" t="n">
+        <v>35</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>50</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H45" t="n">
+        <v>83</v>
+      </c>
+      <c r="I45" t="n">
+        <v>16</v>
+      </c>
+      <c r="J45" t="n">
+        <v>20</v>
+      </c>
+      <c r="K45" t="n">
+        <v>35</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>100</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H46" t="n">
+        <v>83</v>
+      </c>
+      <c r="I46" t="n">
+        <v>16</v>
+      </c>
+      <c r="J46" t="n">
+        <v>20</v>
+      </c>
+      <c r="K46" t="n">
+        <v>35</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.3855421686746988</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="H47" t="n">
+        <v>48</v>
+      </c>
+      <c r="I47" t="n">
+        <v>51</v>
+      </c>
+      <c r="J47" t="n">
+        <v>23</v>
+      </c>
+      <c r="K47" t="n">
+        <v>32</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>0.002057313919067383</v>
+      </c>
+      <c r="N47" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>0.6168831168831169</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.5354330708661418</v>
+      </c>
+      <c r="H48" t="n">
+        <v>61</v>
+      </c>
+      <c r="I48" t="n">
+        <v>38</v>
+      </c>
+      <c r="J48" t="n">
+        <v>21</v>
+      </c>
+      <c r="K48" t="n">
+        <v>34</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>0.001121044158935547</v>
+      </c>
+      <c r="N48" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0.7402597402597403</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.6491228070175439</v>
+      </c>
+      <c r="H49" t="n">
+        <v>77</v>
+      </c>
+      <c r="I49" t="n">
+        <v>22</v>
+      </c>
+      <c r="J49" t="n">
+        <v>18</v>
+      </c>
+      <c r="K49" t="n">
+        <v>37</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>0.0008521080017089844</v>
+      </c>
+      <c r="N49" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H50" t="n">
+        <v>81</v>
+      </c>
+      <c r="I50" t="n">
+        <v>18</v>
+      </c>
+      <c r="J50" t="n">
+        <v>20</v>
+      </c>
+      <c r="K50" t="n">
+        <v>35</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>0.0008509159088134766</v>
+      </c>
+      <c r="N50" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>30</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H51" t="n">
+        <v>81</v>
+      </c>
+      <c r="I51" t="n">
+        <v>18</v>
+      </c>
+      <c r="J51" t="n">
+        <v>20</v>
+      </c>
+      <c r="K51" t="n">
+        <v>35</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>0.001008033752441406</v>
+      </c>
+      <c r="N51" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H52" t="n">
+        <v>81</v>
+      </c>
+      <c r="I52" t="n">
+        <v>18</v>
+      </c>
+      <c r="J52" t="n">
+        <v>20</v>
+      </c>
+      <c r="K52" t="n">
+        <v>35</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="n">
+        <v>0.0009410381317138672</v>
+      </c>
+      <c r="N52" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>100</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.6542056074766355</v>
+      </c>
+      <c r="H53" t="n">
+        <v>82</v>
+      </c>
+      <c r="I53" t="n">
+        <v>17</v>
+      </c>
+      <c r="J53" t="n">
+        <v>20</v>
+      </c>
+      <c r="K53" t="n">
+        <v>35</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>0.0009450912475585938</v>
+      </c>
+      <c r="N53" t="n">
         <v>8.602929272067815</v>
       </c>
     </row>

--- a/results/model_results_diabetes.xlsx
+++ b/results/model_results_diabetes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2432,6 +2432,3718 @@
         <v>8.602929272067815</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H54" t="n">
+        <v>83</v>
+      </c>
+      <c r="I54" t="n">
+        <v>16</v>
+      </c>
+      <c r="J54" t="n">
+        <v>20</v>
+      </c>
+      <c r="K54" t="n">
+        <v>35</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Original_hpt</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>0.7686938127974617</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7120545849918914</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.5722943722943723</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.6317615326537022</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>10</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.006740093231201</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>99</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>55</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.03978490829467773</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>99</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>55</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.04951333999633789</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>99</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>55</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.04069805145263672</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>99</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>55</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.03967785835266113</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>99</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>55</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>10</v>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>0.6547593865679534</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.004761904761904761</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.00909090909090909</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.03952121734619141</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>30</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="n">
+        <v>0.6623376623376623</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="H66" t="n">
+        <v>99</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>52</v>
+      </c>
+      <c r="K66" t="n">
+        <v>3</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>30</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="n">
+        <v>0.6580380750925436</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.07077922077922079</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.1178575712143928</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.03836274147033691</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>50</v>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>0.6948051948051948</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.2545454545454545</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.3733333333333334</v>
+      </c>
+      <c r="H68" t="n">
+        <v>93</v>
+      </c>
+      <c r="I68" t="n">
+        <v>6</v>
+      </c>
+      <c r="J68" t="n">
+        <v>41</v>
+      </c>
+      <c r="K68" t="n">
+        <v>14</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>50</v>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>0.703569539925965</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.6347127872127872</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.346969696969697</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.4434781949437122</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.03794312477111816</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>100</v>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.6464646464646465</v>
+      </c>
+      <c r="H70" t="n">
+        <v>87</v>
+      </c>
+      <c r="I70" t="n">
+        <v>12</v>
+      </c>
+      <c r="J70" t="n">
+        <v>23</v>
+      </c>
+      <c r="K70" t="n">
+        <v>32</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>100</v>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="n">
+        <v>0.7035430988894765</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.6124212715389186</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.4082251082251082</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.4847742608268923</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.04163718223571777</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.4354838709677419</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.4909090909090909</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="H72" t="n">
+        <v>64</v>
+      </c>
+      <c r="I72" t="n">
+        <v>35</v>
+      </c>
+      <c r="J72" t="n">
+        <v>28</v>
+      </c>
+      <c r="K72" t="n">
+        <v>27</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>0.6688311688311688</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.4909090909090909</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="H73" t="n">
+        <v>76</v>
+      </c>
+      <c r="I73" t="n">
+        <v>23</v>
+      </c>
+      <c r="J73" t="n">
+        <v>28</v>
+      </c>
+      <c r="K73" t="n">
+        <v>27</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.6938775510204082</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="H74" t="n">
+        <v>84</v>
+      </c>
+      <c r="I74" t="n">
+        <v>15</v>
+      </c>
+      <c r="J74" t="n">
+        <v>21</v>
+      </c>
+      <c r="K74" t="n">
+        <v>34</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.6542056074766355</v>
+      </c>
+      <c r="H75" t="n">
+        <v>82</v>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>35</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>10</v>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H76" t="n">
+        <v>83</v>
+      </c>
+      <c r="I76" t="n">
+        <v>16</v>
+      </c>
+      <c r="J76" t="n">
+        <v>20</v>
+      </c>
+      <c r="K76" t="n">
+        <v>35</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>30</v>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H77" t="n">
+        <v>83</v>
+      </c>
+      <c r="I77" t="n">
+        <v>16</v>
+      </c>
+      <c r="J77" t="n">
+        <v>20</v>
+      </c>
+      <c r="K77" t="n">
+        <v>35</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>50</v>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H78" t="n">
+        <v>83</v>
+      </c>
+      <c r="I78" t="n">
+        <v>16</v>
+      </c>
+      <c r="J78" t="n">
+        <v>20</v>
+      </c>
+      <c r="K78" t="n">
+        <v>35</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>100</v>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H79" t="n">
+        <v>83</v>
+      </c>
+      <c r="I79" t="n">
+        <v>16</v>
+      </c>
+      <c r="J79" t="n">
+        <v>20</v>
+      </c>
+      <c r="K79" t="n">
+        <v>35</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.3720930232558139</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.4539007092198581</v>
+      </c>
+      <c r="H80" t="n">
+        <v>45</v>
+      </c>
+      <c r="I80" t="n">
+        <v>54</v>
+      </c>
+      <c r="J80" t="n">
+        <v>23</v>
+      </c>
+      <c r="K80" t="n">
+        <v>32</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="n">
+        <v>0.001316070556640625</v>
+      </c>
+      <c r="N80" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.3855421686746988</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="H81" t="n">
+        <v>48</v>
+      </c>
+      <c r="I81" t="n">
+        <v>51</v>
+      </c>
+      <c r="J81" t="n">
+        <v>23</v>
+      </c>
+      <c r="K81" t="n">
+        <v>32</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>0.0008330345153808594</v>
+      </c>
+      <c r="N81" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="n">
+        <v>0.6168831168831169</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.5354330708661418</v>
+      </c>
+      <c r="H82" t="n">
+        <v>61</v>
+      </c>
+      <c r="I82" t="n">
+        <v>38</v>
+      </c>
+      <c r="J82" t="n">
+        <v>21</v>
+      </c>
+      <c r="K82" t="n">
+        <v>34</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>0.00080108642578125</v>
+      </c>
+      <c r="N82" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="n">
+        <v>0.7402597402597403</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.6491228070175439</v>
+      </c>
+      <c r="H83" t="n">
+        <v>77</v>
+      </c>
+      <c r="I83" t="n">
+        <v>22</v>
+      </c>
+      <c r="J83" t="n">
+        <v>18</v>
+      </c>
+      <c r="K83" t="n">
+        <v>37</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>0.0006861686706542969</v>
+      </c>
+      <c r="N83" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H84" t="n">
+        <v>81</v>
+      </c>
+      <c r="I84" t="n">
+        <v>18</v>
+      </c>
+      <c r="J84" t="n">
+        <v>20</v>
+      </c>
+      <c r="K84" t="n">
+        <v>35</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>0.0007681846618652344</v>
+      </c>
+      <c r="N84" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>30</v>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H85" t="n">
+        <v>81</v>
+      </c>
+      <c r="I85" t="n">
+        <v>18</v>
+      </c>
+      <c r="J85" t="n">
+        <v>20</v>
+      </c>
+      <c r="K85" t="n">
+        <v>35</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="n">
+        <v>0.0007469654083251953</v>
+      </c>
+      <c r="N85" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>50</v>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H86" t="n">
+        <v>81</v>
+      </c>
+      <c r="I86" t="n">
+        <v>18</v>
+      </c>
+      <c r="J86" t="n">
+        <v>20</v>
+      </c>
+      <c r="K86" t="n">
+        <v>35</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="n">
+        <v>0.0006561279296875</v>
+      </c>
+      <c r="N86" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>100</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.6542056074766355</v>
+      </c>
+      <c r="H87" t="n">
+        <v>82</v>
+      </c>
+      <c r="I87" t="n">
+        <v>17</v>
+      </c>
+      <c r="J87" t="n">
+        <v>20</v>
+      </c>
+      <c r="K87" t="n">
+        <v>35</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>0.0006570816040039062</v>
+      </c>
+      <c r="N87" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Original_balanced</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="H88" t="n">
+        <v>70</v>
+      </c>
+      <c r="I88" t="n">
+        <v>29</v>
+      </c>
+      <c r="J88" t="n">
+        <v>16</v>
+      </c>
+      <c r="K88" t="n">
+        <v>39</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Original_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>0.7580864197530864</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.7699513341864489</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.7379268292682927</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.7521315494016425</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.904762983322144</v>
+      </c>
+      <c r="N89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.2924528301886792</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.5636363636363636</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.3850931677018634</v>
+      </c>
+      <c r="H90" t="n">
+        <v>24</v>
+      </c>
+      <c r="I90" t="n">
+        <v>75</v>
+      </c>
+      <c r="J90" t="n">
+        <v>24</v>
+      </c>
+      <c r="K90" t="n">
+        <v>31</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>0.5050925925925925</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.5070815030614326</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.4913414634146341</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.4979828720396897</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.05193185806274414</v>
+      </c>
+      <c r="N91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.3557046979865772</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.9636363636363636</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.5196078431372549</v>
+      </c>
+      <c r="H92" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" t="n">
+        <v>96</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="n">
+        <v>53</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>0.5235956790123456</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.524787137713967</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.5382926829268292</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.5297054609173129</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.0494682788848877</v>
+      </c>
+      <c r="N93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="n">
+        <v>0.5844155844155844</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="H94" t="n">
+        <v>70</v>
+      </c>
+      <c r="I94" t="n">
+        <v>29</v>
+      </c>
+      <c r="J94" t="n">
+        <v>35</v>
+      </c>
+      <c r="K94" t="n">
+        <v>20</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="n">
+        <v>0.512608024691358</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.5133915097678164</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.4990243902439025</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.5043343153604443</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.03903579711914062</v>
+      </c>
+      <c r="N95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>0.6558441558441559</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.1636363636363636</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.2535211267605634</v>
+      </c>
+      <c r="H96" t="n">
+        <v>92</v>
+      </c>
+      <c r="I96" t="n">
+        <v>7</v>
+      </c>
+      <c r="J96" t="n">
+        <v>46</v>
+      </c>
+      <c r="K96" t="n">
+        <v>9</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>5</v>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>0.5086882716049382</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.5080551717710621</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.506219512195122</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.5048097594241943</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.04921126365661621</v>
+      </c>
+      <c r="N97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>10</v>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>0.6883116883116883</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.1636363636363636</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="H98" t="n">
+        <v>97</v>
+      </c>
+      <c r="I98" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" t="n">
+        <v>46</v>
+      </c>
+      <c r="K98" t="n">
+        <v>9</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>10</v>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="n">
+        <v>0.5326543209876544</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.5339051868753881</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.5016463414634147</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.5151991797775588</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.04137969017028809</v>
+      </c>
+      <c r="N99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>30</v>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="n">
+        <v>0.7337662337662337</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.594059405940594</v>
+      </c>
+      <c r="H100" t="n">
+        <v>83</v>
+      </c>
+      <c r="I100" t="n">
+        <v>16</v>
+      </c>
+      <c r="J100" t="n">
+        <v>25</v>
+      </c>
+      <c r="K100" t="n">
+        <v>30</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>30</v>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="n">
+        <v>0.5822067901234568</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.5876833482718898</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.5659146341463415</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.5750093570321206</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.04805302619934082</v>
+      </c>
+      <c r="N101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>50</v>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.6545454545454545</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="H102" t="n">
+        <v>73</v>
+      </c>
+      <c r="I102" t="n">
+        <v>26</v>
+      </c>
+      <c r="J102" t="n">
+        <v>19</v>
+      </c>
+      <c r="K102" t="n">
+        <v>36</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>50</v>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>0.6745987654320988</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.6801925363121885</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.663170731707317</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.6700756115529123</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.03871297836303711</v>
+      </c>
+      <c r="N103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Input_balanced</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>100</v>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="n">
+        <v>0.7207792207792207</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.6504065040650406</v>
+      </c>
+      <c r="H104" t="n">
+        <v>71</v>
+      </c>
+      <c r="I104" t="n">
+        <v>28</v>
+      </c>
+      <c r="J104" t="n">
+        <v>15</v>
+      </c>
+      <c r="K104" t="n">
+        <v>40</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Input_hpt_balanced</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>100</v>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="n">
+        <v>0.7033179012345678</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.7160185157323167</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.6833536585365854</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.6972012029301897</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.05097293853759766</v>
+      </c>
+      <c r="N105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="n">
+        <v>0.6103896103896104</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.4603174603174603</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.5272727272727272</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.4915254237288136</v>
+      </c>
+      <c r="H106" t="n">
+        <v>65</v>
+      </c>
+      <c r="I106" t="n">
+        <v>34</v>
+      </c>
+      <c r="J106" t="n">
+        <v>26</v>
+      </c>
+      <c r="K106" t="n">
+        <v>29</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="n">
+        <v>0.6883116883116883</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H107" t="n">
+        <v>66</v>
+      </c>
+      <c r="I107" t="n">
+        <v>33</v>
+      </c>
+      <c r="J107" t="n">
+        <v>15</v>
+      </c>
+      <c r="K107" t="n">
+        <v>40</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="H108" t="n">
+        <v>70</v>
+      </c>
+      <c r="I108" t="n">
+        <v>29</v>
+      </c>
+      <c r="J108" t="n">
+        <v>16</v>
+      </c>
+      <c r="K108" t="n">
+        <v>39</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>5</v>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="H109" t="n">
+        <v>70</v>
+      </c>
+      <c r="I109" t="n">
+        <v>29</v>
+      </c>
+      <c r="J109" t="n">
+        <v>16</v>
+      </c>
+      <c r="K109" t="n">
+        <v>39</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>10</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="H110" t="n">
+        <v>70</v>
+      </c>
+      <c r="I110" t="n">
+        <v>29</v>
+      </c>
+      <c r="J110" t="n">
+        <v>16</v>
+      </c>
+      <c r="K110" t="n">
+        <v>39</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>30</v>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="H111" t="n">
+        <v>70</v>
+      </c>
+      <c r="I111" t="n">
+        <v>29</v>
+      </c>
+      <c r="J111" t="n">
+        <v>16</v>
+      </c>
+      <c r="K111" t="n">
+        <v>39</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>50</v>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="H112" t="n">
+        <v>70</v>
+      </c>
+      <c r="I112" t="n">
+        <v>29</v>
+      </c>
+      <c r="J112" t="n">
+        <v>16</v>
+      </c>
+      <c r="K112" t="n">
+        <v>39</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Output_balanced</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>100</v>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="H113" t="n">
+        <v>70</v>
+      </c>
+      <c r="I113" t="n">
+        <v>29</v>
+      </c>
+      <c r="J113" t="n">
+        <v>16</v>
+      </c>
+      <c r="K113" t="n">
+        <v>39</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="n">
+        <v>0.512987012987013</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.3780487804878049</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.5636363636363636</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.4525547445255474</v>
+      </c>
+      <c r="H114" t="n">
+        <v>48</v>
+      </c>
+      <c r="I114" t="n">
+        <v>51</v>
+      </c>
+      <c r="J114" t="n">
+        <v>24</v>
+      </c>
+      <c r="K114" t="n">
+        <v>31</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>0.001334190368652344</v>
+      </c>
+      <c r="N114" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="n">
+        <v>0.538961038961039</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.4024390243902439</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.4817518248175183</v>
+      </c>
+      <c r="H115" t="n">
+        <v>50</v>
+      </c>
+      <c r="I115" t="n">
+        <v>49</v>
+      </c>
+      <c r="J115" t="n">
+        <v>22</v>
+      </c>
+      <c r="K115" t="n">
+        <v>33</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="n">
+        <v>0.002106904983520508</v>
+      </c>
+      <c r="N115" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="n">
+        <v>0.6298701298701299</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.4878048780487805</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.583941605839416</v>
+      </c>
+      <c r="H116" t="n">
+        <v>57</v>
+      </c>
+      <c r="I116" t="n">
+        <v>42</v>
+      </c>
+      <c r="J116" t="n">
+        <v>15</v>
+      </c>
+      <c r="K116" t="n">
+        <v>40</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>0.002053976058959961</v>
+      </c>
+      <c r="N116" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="n">
+        <v>0.7012987012987013</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5616438356164384</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.7454545454545455</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="H117" t="n">
+        <v>67</v>
+      </c>
+      <c r="I117" t="n">
+        <v>32</v>
+      </c>
+      <c r="J117" t="n">
+        <v>14</v>
+      </c>
+      <c r="K117" t="n">
+        <v>41</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="n">
+        <v>0.001795053482055664</v>
+      </c>
+      <c r="N117" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>10</v>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="n">
+        <v>0.6948051948051948</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6299212598425197</v>
+      </c>
+      <c r="H118" t="n">
+        <v>67</v>
+      </c>
+      <c r="I118" t="n">
+        <v>32</v>
+      </c>
+      <c r="J118" t="n">
+        <v>15</v>
+      </c>
+      <c r="K118" t="n">
+        <v>40</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>0.0009210109710693359</v>
+      </c>
+      <c r="N118" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>30</v>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.582089552238806</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="H119" t="n">
+        <v>71</v>
+      </c>
+      <c r="I119" t="n">
+        <v>28</v>
+      </c>
+      <c r="J119" t="n">
+        <v>16</v>
+      </c>
+      <c r="K119" t="n">
+        <v>39</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>0.001503944396972656</v>
+      </c>
+      <c r="N119" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>50</v>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="H120" t="n">
+        <v>70</v>
+      </c>
+      <c r="I120" t="n">
+        <v>29</v>
+      </c>
+      <c r="J120" t="n">
+        <v>16</v>
+      </c>
+      <c r="K120" t="n">
+        <v>39</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>0.001059055328369141</v>
+      </c>
+      <c r="N120" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Internal_balanced</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>100</v>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="n">
+        <v>0.7077922077922078</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.5735294117647058</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="H121" t="n">
+        <v>70</v>
+      </c>
+      <c r="I121" t="n">
+        <v>29</v>
+      </c>
+      <c r="J121" t="n">
+        <v>16</v>
+      </c>
+      <c r="K121" t="n">
+        <v>39</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>0.0008866786956787109</v>
+      </c>
+      <c r="N121" t="n">
+        <v>8.381499661996164</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H122" t="n">
+        <v>83</v>
+      </c>
+      <c r="I122" t="n">
+        <v>16</v>
+      </c>
+      <c r="J122" t="n">
+        <v>20</v>
+      </c>
+      <c r="K122" t="n">
+        <v>35</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Original_hpt</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="n">
+        <v>0.767119818739171</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.708249734136831</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.5679955703211517</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.6293664285993052</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.887562036514282</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>99</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>55</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.05171895027160645</v>
+      </c>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>99</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>55</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.0399329662322998</v>
+      </c>
+      <c r="N127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>5</v>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="n">
+        <v>0.6753246753246753</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="H128" t="n">
+        <v>99</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>50</v>
+      </c>
+      <c r="K128" t="n">
+        <v>5</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>5</v>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="n">
+        <v>0.6645425700687466</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.5513702963702964</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.2348484848484849</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3276751946607342</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.04051923751831055</v>
+      </c>
+      <c r="N129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>10</v>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.4727272727272727</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.5977011494252874</v>
+      </c>
+      <c r="H130" t="n">
+        <v>93</v>
+      </c>
+      <c r="I130" t="n">
+        <v>6</v>
+      </c>
+      <c r="J130" t="n">
+        <v>29</v>
+      </c>
+      <c r="K130" t="n">
+        <v>26</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>10</v>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="n">
+        <v>0.7152035959809624</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.6583997873471558</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3854978354978356</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.4824891774891774</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.03909778594970703</v>
+      </c>
+      <c r="N131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>30</v>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.6476190476190476</v>
+      </c>
+      <c r="H132" t="n">
+        <v>83</v>
+      </c>
+      <c r="I132" t="n">
+        <v>16</v>
+      </c>
+      <c r="J132" t="n">
+        <v>21</v>
+      </c>
+      <c r="K132" t="n">
+        <v>34</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>30</v>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="n">
+        <v>0.7607086197778953</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.6931432748538012</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.5640692640692639</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.6200182368603422</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.03908109664916992</v>
+      </c>
+      <c r="N133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>50</v>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.6476190476190476</v>
+      </c>
+      <c r="H134" t="n">
+        <v>83</v>
+      </c>
+      <c r="I134" t="n">
+        <v>16</v>
+      </c>
+      <c r="J134" t="n">
+        <v>21</v>
+      </c>
+      <c r="K134" t="n">
+        <v>34</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>50</v>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="n">
+        <v>0.7541248016922263</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.6864880952380952</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.554112554112554</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.6109334546497577</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="n">
+        <v>10</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.03956413269042969</v>
+      </c>
+      <c r="N135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>100</v>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H136" t="n">
+        <v>81</v>
+      </c>
+      <c r="I136" t="n">
+        <v>18</v>
+      </c>
+      <c r="J136" t="n">
+        <v>20</v>
+      </c>
+      <c r="K136" t="n">
+        <v>35</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>100</v>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="n">
+        <v>0.7686144896879956</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.7060631860399662</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.5764069264069264</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.6314643523565218</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="n">
+        <v>10</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.04186606407165527</v>
+      </c>
+      <c r="N137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.6037735849056604</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="H138" t="n">
+        <v>78</v>
+      </c>
+      <c r="I138" t="n">
+        <v>21</v>
+      </c>
+      <c r="J138" t="n">
+        <v>23</v>
+      </c>
+      <c r="K138" t="n">
+        <v>32</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H139" t="n">
+        <v>83</v>
+      </c>
+      <c r="I139" t="n">
+        <v>16</v>
+      </c>
+      <c r="J139" t="n">
+        <v>20</v>
+      </c>
+      <c r="K139" t="n">
+        <v>35</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>5</v>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H140" t="n">
+        <v>83</v>
+      </c>
+      <c r="I140" t="n">
+        <v>16</v>
+      </c>
+      <c r="J140" t="n">
+        <v>20</v>
+      </c>
+      <c r="K140" t="n">
+        <v>35</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>10</v>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H141" t="n">
+        <v>83</v>
+      </c>
+      <c r="I141" t="n">
+        <v>16</v>
+      </c>
+      <c r="J141" t="n">
+        <v>20</v>
+      </c>
+      <c r="K141" t="n">
+        <v>35</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>30</v>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H142" t="n">
+        <v>83</v>
+      </c>
+      <c r="I142" t="n">
+        <v>16</v>
+      </c>
+      <c r="J142" t="n">
+        <v>20</v>
+      </c>
+      <c r="K142" t="n">
+        <v>35</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>50</v>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H143" t="n">
+        <v>83</v>
+      </c>
+      <c r="I143" t="n">
+        <v>16</v>
+      </c>
+      <c r="J143" t="n">
+        <v>20</v>
+      </c>
+      <c r="K143" t="n">
+        <v>35</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>100</v>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H144" t="n">
+        <v>83</v>
+      </c>
+      <c r="I144" t="n">
+        <v>16</v>
+      </c>
+      <c r="J144" t="n">
+        <v>20</v>
+      </c>
+      <c r="K144" t="n">
+        <v>35</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.3855421686746988</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="H145" t="n">
+        <v>48</v>
+      </c>
+      <c r="I145" t="n">
+        <v>51</v>
+      </c>
+      <c r="J145" t="n">
+        <v>23</v>
+      </c>
+      <c r="K145" t="n">
+        <v>32</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="n">
+        <v>0.001335620880126953</v>
+      </c>
+      <c r="N145" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="n">
+        <v>0.6168831168831169</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.5354330708661418</v>
+      </c>
+      <c r="H146" t="n">
+        <v>61</v>
+      </c>
+      <c r="I146" t="n">
+        <v>38</v>
+      </c>
+      <c r="J146" t="n">
+        <v>21</v>
+      </c>
+      <c r="K146" t="n">
+        <v>34</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="n">
+        <v>0.0009002685546875</v>
+      </c>
+      <c r="N146" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>5</v>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="n">
+        <v>0.7402597402597403</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.6491228070175439</v>
+      </c>
+      <c r="H147" t="n">
+        <v>77</v>
+      </c>
+      <c r="I147" t="n">
+        <v>22</v>
+      </c>
+      <c r="J147" t="n">
+        <v>18</v>
+      </c>
+      <c r="K147" t="n">
+        <v>37</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="n">
+        <v>0.0009558200836181641</v>
+      </c>
+      <c r="N147" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>10</v>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H148" t="n">
+        <v>81</v>
+      </c>
+      <c r="I148" t="n">
+        <v>18</v>
+      </c>
+      <c r="J148" t="n">
+        <v>20</v>
+      </c>
+      <c r="K148" t="n">
+        <v>35</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="n">
+        <v>0.0008580684661865234</v>
+      </c>
+      <c r="N148" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>30</v>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H149" t="n">
+        <v>81</v>
+      </c>
+      <c r="I149" t="n">
+        <v>18</v>
+      </c>
+      <c r="J149" t="n">
+        <v>20</v>
+      </c>
+      <c r="K149" t="n">
+        <v>35</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="n">
+        <v>0.0006880760192871094</v>
+      </c>
+      <c r="N149" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>50</v>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H150" t="n">
+        <v>81</v>
+      </c>
+      <c r="I150" t="n">
+        <v>18</v>
+      </c>
+      <c r="J150" t="n">
+        <v>20</v>
+      </c>
+      <c r="K150" t="n">
+        <v>35</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="n">
+        <v>0.0006530284881591797</v>
+      </c>
+      <c r="N150" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>100</v>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.6542056074766355</v>
+      </c>
+      <c r="H151" t="n">
+        <v>82</v>
+      </c>
+      <c r="I151" t="n">
+        <v>17</v>
+      </c>
+      <c r="J151" t="n">
+        <v>20</v>
+      </c>
+      <c r="K151" t="n">
+        <v>35</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="n">
+        <v>0.0007009506225585938</v>
+      </c>
+      <c r="N151" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/model_results_diabetes.xlsx
+++ b/results/model_results_diabetes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6144,6 +6144,1294 @@
         <v>8.602929272067815</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H152" t="n">
+        <v>83</v>
+      </c>
+      <c r="I152" t="n">
+        <v>16</v>
+      </c>
+      <c r="J152" t="n">
+        <v>20</v>
+      </c>
+      <c r="K152" t="n">
+        <v>35</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Original_hpt</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="n">
+        <v>0.7686938127974617</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.7120545849918914</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.5722943722943723</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.6317615326537022</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="n">
+        <v>10</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1.687085866928101</v>
+      </c>
+      <c r="N153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>99</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>55</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0.05137729644775391</v>
+      </c>
+      <c r="N155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>99</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>55</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0.03937101364135742</v>
+      </c>
+      <c r="N157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>99</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>55</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0.04086828231811523</v>
+      </c>
+      <c r="N159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>99</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>55</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>5</v>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="n">
+        <v>0.6531200423056583</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0.04784297943115234</v>
+      </c>
+      <c r="N161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>10</v>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>99</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>55</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>10</v>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="n">
+        <v>0.6547593865679534</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.004761904761904761</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.00909090909090909</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0.03853487968444824</v>
+      </c>
+      <c r="N163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>30</v>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="n">
+        <v>0.6623376623376623</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="H164" t="n">
+        <v>99</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>52</v>
+      </c>
+      <c r="K164" t="n">
+        <v>3</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>30</v>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="n">
+        <v>0.6580380750925436</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.07077922077922079</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.1178575712143928</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0.04158687591552734</v>
+      </c>
+      <c r="N165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>50</v>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="n">
+        <v>0.6948051948051948</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.2545454545454545</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.3733333333333334</v>
+      </c>
+      <c r="H166" t="n">
+        <v>93</v>
+      </c>
+      <c r="I166" t="n">
+        <v>6</v>
+      </c>
+      <c r="J166" t="n">
+        <v>41</v>
+      </c>
+      <c r="K166" t="n">
+        <v>14</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>50</v>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="n">
+        <v>0.703569539925965</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.6347127872127872</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.346969696969697</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.4434781949437122</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0.03885841369628906</v>
+      </c>
+      <c r="N167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>100</v>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.6464646464646465</v>
+      </c>
+      <c r="H168" t="n">
+        <v>87</v>
+      </c>
+      <c r="I168" t="n">
+        <v>12</v>
+      </c>
+      <c r="J168" t="n">
+        <v>23</v>
+      </c>
+      <c r="K168" t="n">
+        <v>32</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Input_hpt</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>100</v>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="n">
+        <v>0.7035430988894765</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.6124212715389186</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.4082251082251082</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.4847742608268923</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0.04053807258605957</v>
+      </c>
+      <c r="N169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.4354838709677419</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.4909090909090909</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="H170" t="n">
+        <v>64</v>
+      </c>
+      <c r="I170" t="n">
+        <v>35</v>
+      </c>
+      <c r="J170" t="n">
+        <v>28</v>
+      </c>
+      <c r="K170" t="n">
+        <v>27</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="n">
+        <v>0.6688311688311688</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.4909090909090909</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="H171" t="n">
+        <v>76</v>
+      </c>
+      <c r="I171" t="n">
+        <v>23</v>
+      </c>
+      <c r="J171" t="n">
+        <v>28</v>
+      </c>
+      <c r="K171" t="n">
+        <v>27</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.6938775510204082</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="H172" t="n">
+        <v>84</v>
+      </c>
+      <c r="I172" t="n">
+        <v>15</v>
+      </c>
+      <c r="J172" t="n">
+        <v>21</v>
+      </c>
+      <c r="K172" t="n">
+        <v>34</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>5</v>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.6542056074766355</v>
+      </c>
+      <c r="H173" t="n">
+        <v>82</v>
+      </c>
+      <c r="I173" t="n">
+        <v>17</v>
+      </c>
+      <c r="J173" t="n">
+        <v>20</v>
+      </c>
+      <c r="K173" t="n">
+        <v>35</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>10</v>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H174" t="n">
+        <v>83</v>
+      </c>
+      <c r="I174" t="n">
+        <v>16</v>
+      </c>
+      <c r="J174" t="n">
+        <v>20</v>
+      </c>
+      <c r="K174" t="n">
+        <v>35</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>30</v>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H175" t="n">
+        <v>83</v>
+      </c>
+      <c r="I175" t="n">
+        <v>16</v>
+      </c>
+      <c r="J175" t="n">
+        <v>20</v>
+      </c>
+      <c r="K175" t="n">
+        <v>35</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>50</v>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H176" t="n">
+        <v>83</v>
+      </c>
+      <c r="I176" t="n">
+        <v>16</v>
+      </c>
+      <c r="J176" t="n">
+        <v>20</v>
+      </c>
+      <c r="K176" t="n">
+        <v>35</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>100</v>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="n">
+        <v>0.7662337662337663</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="H177" t="n">
+        <v>83</v>
+      </c>
+      <c r="I177" t="n">
+        <v>16</v>
+      </c>
+      <c r="J177" t="n">
+        <v>20</v>
+      </c>
+      <c r="K177" t="n">
+        <v>35</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.3720930232558139</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.4539007092198581</v>
+      </c>
+      <c r="H178" t="n">
+        <v>45</v>
+      </c>
+      <c r="I178" t="n">
+        <v>54</v>
+      </c>
+      <c r="J178" t="n">
+        <v>23</v>
+      </c>
+      <c r="K178" t="n">
+        <v>32</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="n">
+        <v>0.0009799003601074219</v>
+      </c>
+      <c r="N178" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.3855421686746988</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="H179" t="n">
+        <v>48</v>
+      </c>
+      <c r="I179" t="n">
+        <v>51</v>
+      </c>
+      <c r="J179" t="n">
+        <v>23</v>
+      </c>
+      <c r="K179" t="n">
+        <v>32</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="n">
+        <v>0.0008580684661865234</v>
+      </c>
+      <c r="N179" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="n">
+        <v>0.6168831168831169</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.5354330708661418</v>
+      </c>
+      <c r="H180" t="n">
+        <v>61</v>
+      </c>
+      <c r="I180" t="n">
+        <v>38</v>
+      </c>
+      <c r="J180" t="n">
+        <v>21</v>
+      </c>
+      <c r="K180" t="n">
+        <v>34</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="n">
+        <v>0.0008058547973632812</v>
+      </c>
+      <c r="N180" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="n">
+        <v>0.7402597402597403</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.6491228070175439</v>
+      </c>
+      <c r="H181" t="n">
+        <v>77</v>
+      </c>
+      <c r="I181" t="n">
+        <v>22</v>
+      </c>
+      <c r="J181" t="n">
+        <v>18</v>
+      </c>
+      <c r="K181" t="n">
+        <v>37</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="n">
+        <v>0.0007779598236083984</v>
+      </c>
+      <c r="N181" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>10</v>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H182" t="n">
+        <v>81</v>
+      </c>
+      <c r="I182" t="n">
+        <v>18</v>
+      </c>
+      <c r="J182" t="n">
+        <v>20</v>
+      </c>
+      <c r="K182" t="n">
+        <v>35</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="n">
+        <v>0.0006730556488037109</v>
+      </c>
+      <c r="N182" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>30</v>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H183" t="n">
+        <v>81</v>
+      </c>
+      <c r="I183" t="n">
+        <v>18</v>
+      </c>
+      <c r="J183" t="n">
+        <v>20</v>
+      </c>
+      <c r="K183" t="n">
+        <v>35</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="n">
+        <v>0.0008141994476318359</v>
+      </c>
+      <c r="N183" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>50</v>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="H184" t="n">
+        <v>81</v>
+      </c>
+      <c r="I184" t="n">
+        <v>18</v>
+      </c>
+      <c r="J184" t="n">
+        <v>20</v>
+      </c>
+      <c r="K184" t="n">
+        <v>35</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="n">
+        <v>0.0006849765777587891</v>
+      </c>
+      <c r="N184" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>100</v>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.6542056074766355</v>
+      </c>
+      <c r="H185" t="n">
+        <v>82</v>
+      </c>
+      <c r="I185" t="n">
+        <v>17</v>
+      </c>
+      <c r="J185" t="n">
+        <v>20</v>
+      </c>
+      <c r="K185" t="n">
+        <v>35</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="n">
+        <v>0.0006861686706542969</v>
+      </c>
+      <c r="N185" t="n">
+        <v>8.602929272067815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
